--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487615_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487615_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7277</v>
+        <v>3.9964</v>
       </c>
       <c r="E2" t="n">
-        <v>4.773</v>
+        <v>3.5323</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9547</v>
+        <v>0.4642</v>
       </c>
       <c r="G2" t="n">
         <v>1.965</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4807</v>
+        <v>1.7494</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3553</v>
+        <v>1.1145</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1254</v>
+        <v>0.6348</v>
       </c>
       <c r="V2" t="n">
         <v>0.2821</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2778</v>
+        <v>1.7453</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1238</v>
+        <v>4.346</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.846</v>
+        <v>-2.6007</v>
       </c>
       <c r="G3" t="n">
         <v>-1.3141</v>
@@ -688,13 +688,13 @@
         <v>2.7164</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6485</v>
+        <v>0.819</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8109</v>
+        <v>0.4113</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1624</v>
+        <v>0.4077</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2821</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.164</v>
+        <v>0.1912</v>
       </c>
       <c r="E4" t="n">
         <v>-0.1211</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2851</v>
+        <v>0.3124</v>
       </c>
       <c r="G4" t="n">
         <v>0.5339</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3699</v>
+        <v>-0.3426</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1211</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2488</v>
+        <v>-0.2215</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3869</v>
+        <v>-1.1807</v>
       </c>
       <c r="E6" t="n">
-        <v>0.611</v>
+        <v>0.8717</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9979</v>
+        <v>-2.0524</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2223</v>
@@ -922,13 +922,13 @@
         <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3885</v>
+        <v>-0.1822</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.157</v>
+        <v>0.1037</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2315</v>
+        <v>-0.286</v>
       </c>
       <c r="V6" t="n">
         <v>0.6119</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4315</v>
+        <v>-1.4282</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7188</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7128</v>
+        <v>-0.8108</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.5962</v>
+        <v>-3.1024</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4889</v>
+        <v>-2.8588</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1073</v>
+        <v>-0.2436</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8298</v>
+        <v>0.1596</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9516</v>
+        <v>-1.104</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1218</v>
+        <v>1.2635</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7664</v>
+        <v>-3.262</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5374</v>
+        <v>-1.7549</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.229</v>
+        <v>-1.5071</v>
       </c>
       <c r="P7" t="n">
         <v>0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3582</v>
+        <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3109</v>
+        <v>0.916</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2752</v>
+        <v>0.5992</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0357</v>
+        <v>0.3169</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6597</v>
+        <v>0.5642</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8692</v>
+        <v>-1.5961</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1738</v>
+        <v>1.4741</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.043</v>
+        <v>-3.0702</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2139</v>
@@ -1078,13 +1078,13 @@
         <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>0.491</v>
+        <v>0.7641</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3409</v>
+        <v>0.6412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1501</v>
+        <v>0.1228</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1761</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9973</v>
+        <v>-1.7065</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1987</v>
+        <v>-1.0986</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7986</v>
+        <v>-0.6078</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9305</v>
@@ -1156,13 +1156,13 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4549</v>
+        <v>-0.164</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0482</v>
+        <v>0.0519</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4067</v>
+        <v>-0.2159</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.18</v>
+        <v>-2.028</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1785</v>
+        <v>-0.831</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0015</v>
+        <v>-1.1969</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1024</v>
+        <v>-2.2011</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8588</v>
+        <v>-0.332</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2436</v>
+        <v>-1.8691</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1596</v>
+        <v>-0.2641</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.104</v>
+        <v>0.5149</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2635</v>
+        <v>-0.779</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.262</v>
+        <v>-1.937</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7549</v>
+        <v>-0.8469</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5071</v>
+        <v>-1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>0.194</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1344</v>
+        <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1642</v>
+        <v>0.9194</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0381</v>
+        <v>0.5078</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1261</v>
+        <v>0.4116</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5642</v>
+        <v>0.6119</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5642</v>
+        <v>1.8358</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4979</v>
+        <v>-2.263</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1919</v>
+        <v>-1.6592</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.306</v>
+        <v>-0.6038</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2011</v>
+        <v>-3.5962</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.332</v>
+        <v>-2.4889</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8691</v>
+        <v>-1.1073</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2641</v>
+        <v>-0.8298</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5149</v>
+        <v>-0.9516</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.779</v>
+        <v>0.1218</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.937</v>
+        <v>-2.7664</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8469</v>
+        <v>-1.5374</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.09</v>
+        <v>-1.229</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9105</v>
+        <v>-1.1642</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4495</v>
+        <v>0.4795</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1469</v>
+        <v>0.3348</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3026</v>
+        <v>0.1447</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6119</v>
+        <v>0.6597</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2239</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3045</v>
+        <v>-5.3925</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6813</v>
+        <v>-1.6603</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6232</v>
+        <v>-3.7322</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5229</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3513</v>
+        <v>0.2633</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0134</v>
+        <v>0.0345</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3378</v>
+        <v>0.2288</v>
       </c>
       <c r="V12" t="n">
         <v>0.3299</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.563</v>
+        <v>-6.7933</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4876</v>
+        <v>-4.5271</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0754</v>
+        <v>-2.2662</v>
       </c>
       <c r="G13" t="n">
         <v>-6.1821</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>0.843</v>
+        <v>0.6127</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1951</v>
+        <v>0.1556</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6478</v>
+        <v>0.4571</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2239</v>
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.9979</v>
+        <v>-17.3925</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6848</v>
+        <v>-1.0791</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.3132</v>
+        <v>-16.313</v>
       </c>
       <c r="G14" t="n">
         <v>-19.187</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.7012</v>
+        <v>-5.701199999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-13.486</v>
       </c>
       <c r="J14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.200000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>8.337599999999998</v>
+        <v>8.3376</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8622999999999998</v>
+        <v>0.8622999999999994</v>
       </c>
       <c r="M14" t="n">
         <v>-28.387</v>
@@ -1546,13 +1546,13 @@
         <v>15.5228</v>
       </c>
       <c r="S14" t="n">
-        <v>4.9742</v>
+        <v>5.58</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1066</v>
+        <v>3.7123</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8674</v>
+        <v>1.8675</v>
       </c>
       <c r="V14" t="n">
         <v>0.09549999999999992</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8839</v>
+        <v>6.7843</v>
       </c>
       <c r="E15" t="n">
-        <v>6.546</v>
+        <v>7.1466</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.662</v>
+        <v>-0.3622</v>
       </c>
       <c r="G15" t="n">
         <v>4.8714</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5516</v>
+        <v>0.3488</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7145</v>
+        <v>-0.1139</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1629</v>
+        <v>0.4627</v>
       </c>
       <c r="V15" t="n">
         <v>1.1761</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>A. JIMÉNEZ BARRETO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5112</v>
+        <v>4.5798</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3191</v>
+        <v>3.5804</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1921</v>
+        <v>0.9994</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2023</v>
+        <v>4.0565</v>
       </c>
       <c r="H16" t="n">
-        <v>1.52</v>
+        <v>-0.8156</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6822</v>
+        <v>4.8722</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7552</v>
+        <v>3.9859</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7837</v>
+        <v>-0.5026</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9715</v>
+        <v>4.4885</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5528999999999999</v>
+        <v>0.0706</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2637</v>
+        <v>-0.3131</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2892</v>
+        <v>0.3837</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3284</v>
+        <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3089</v>
+        <v>-0.8827</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1077</v>
+        <v>-0.4055</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4166</v>
+        <v>-0.4772</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6119</v>
+        <v>0.0478</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. JIMÉNEZ BARRETO</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.061</v>
+        <v>4.2292</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3802</v>
+        <v>2.1189</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6808</v>
+        <v>2.1103</v>
       </c>
       <c r="G17" t="n">
-        <v>4.0565</v>
+        <v>3.2023</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8156</v>
+        <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8722</v>
+        <v>1.6822</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9859</v>
+        <v>3.7552</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5026</v>
+        <v>1.7837</v>
       </c>
       <c r="L17" t="n">
-        <v>4.4885</v>
+        <v>1.9715</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0706</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3131</v>
+        <v>-0.2637</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3837</v>
+        <v>-0.2892</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3582</v>
+        <v>2.3284</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4015</v>
+        <v>0.0269</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6057</v>
+        <v>-0.3079</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7958</v>
+        <v>0.3348</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0478</v>
+        <v>0.6119</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>S. KONE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8526</v>
+        <v>3.1414</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6301</v>
+        <v>2.7096</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7775</v>
+        <v>0.4318</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1969</v>
+        <v>2.769</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2688</v>
+        <v>1.0339</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9282</v>
+        <v>1.7351</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4287</v>
+        <v>3.7453</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6117</v>
+        <v>2.1215</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8169999999999999</v>
+        <v>1.6239</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2317</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3429</v>
+        <v>-1.0875</v>
       </c>
       <c r="O18" t="n">
         <v>0.1112</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3284</v>
+        <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0906</v>
+        <v>-0.2097</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5596</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6503</v>
+        <v>-0.1441</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. KONE</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6414</v>
+        <v>2.9132</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9097</v>
+        <v>3.1296</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2684</v>
+        <v>-0.2164</v>
       </c>
       <c r="G19" t="n">
-        <v>2.769</v>
+        <v>2.1969</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0339</v>
+        <v>1.2688</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7351</v>
+        <v>0.9282</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7453</v>
+        <v>3.4287</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1215</v>
+        <v>2.6117</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6239</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-1.2317</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0875</v>
+        <v>-1.3429</v>
       </c>
       <c r="O19" t="n">
         <v>0.1112</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5523</v>
+        <v>2.3284</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7097</v>
+        <v>-0.03</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1346</v>
+        <v>0.0591</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.0891</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6783</v>
+        <v>1.4814</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3113</v>
+        <v>1.011</v>
       </c>
       <c r="F20" t="n">
-        <v>0.367</v>
+        <v>0.4704</v>
       </c>
       <c r="G20" t="n">
         <v>2.6128</v>
@@ -2014,13 +2014,13 @@
         <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0357</v>
+        <v>-0.1612</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1828</v>
+        <v>-0.1175</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1471</v>
+        <v>-0.0437</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>J. LARREA IBARBURU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3238</v>
+        <v>1.2449</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7513</v>
+        <v>1.314</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5725</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3071</v>
+        <v>2.36</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2958</v>
+        <v>-0.1458</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6028</v>
+        <v>2.5059</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8845</v>
+        <v>3.7862</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8033</v>
+        <v>1.1246</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08119999999999999</v>
+        <v>2.6616</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1916</v>
+        <v>-1.4262</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5075</v>
+        <v>-1.2704</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.1557</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8443</v>
+        <v>-0.7091</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2146</v>
+        <v>-0.408</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6297</v>
+        <v>-0.3011</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9896</v>
+        <v>0.5642</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3776</v>
+        <v>0.8462</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6119</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. LARREA IBARBURU</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1288</v>
+        <v>0.1047</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8135</v>
+        <v>-0.2497</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6847</v>
+        <v>0.3544</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>-0.3071</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1458</v>
+        <v>0.2958</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5059</v>
+        <v>-0.6028</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7862</v>
+        <v>0.8845</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1246</v>
+        <v>0.8033</v>
       </c>
       <c r="L22" t="n">
-        <v>2.6616</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4262</v>
+        <v>-1.1916</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2704</v>
+        <v>-0.5075</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1557</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P22" t="n">
+        <v>0.7761</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8252</v>
+        <v>0.6253</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9085</v>
+        <v>0.2136</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9167999999999999</v>
+        <v>0.4116</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5642</v>
+        <v>-0.9896</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8462</v>
+        <v>-0.3776</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2821</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.722</v>
+        <v>-0.8272</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4633</v>
+        <v>-0.8627</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2587</v>
+        <v>0.0355</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3729</v>
@@ -2248,13 +2248,13 @@
         <v>3.1045</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2313</v>
+        <v>-0.3365</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9567</v>
+        <v>-0.3561</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2745</v>
+        <v>0.0197</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2821</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.361</v>
+        <v>-2.9846</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8847</v>
+        <v>-3.5844</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5999</v>
       </c>
       <c r="G24" t="n">
         <v>-1.202</v>
@@ -2326,13 +2326,13 @@
         <v>1.7463</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.353</v>
+        <v>-0.9766</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6662</v>
+        <v>-0.3659</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6868</v>
+        <v>-0.6107</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6119</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>17.998</v>
+        <v>20.6671</v>
       </c>
       <c r="E25" t="n">
-        <v>16.3132</v>
+        <v>16.3133</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6848</v>
+        <v>4.354</v>
       </c>
       <c r="G25" t="n">
         <v>19.1869</v>
@@ -2404,13 +2404,13 @@
         <v>19.4032</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.974</v>
+        <v>-2.3048</v>
       </c>
       <c r="T25" t="n">
         <v>-1.8677</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.1064</v>
+        <v>-0.4371</v>
       </c>
       <c r="V25" t="n">
         <v>-0.09550000000000025</v>
